--- a/docs/ai_transport_code_map.xlsx
+++ b/docs/ai_transport_code_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yingyuel\Desktop\2.ai_tranport\ai_transport\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF712F36-C62B-46EC-835F-DB89B26958CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374CE555-F80F-4C60-A1C9-2B2686FA2599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53652" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="py document" sheetId="1" r:id="rId1"/>
@@ -562,9 +562,6 @@
     <t>把 TransportGymWrapper 转换成 Stable-Baselines3 DQN 可训练的单智能体环境。</t>
   </si>
   <si>
-    <t>action_masks: 返回合法动作；_format_observation/_flatten_observation: 整理 DQN 输入；reset: 重置并推进到决策点；step: 执行 DQN action 并自动推进内部阶段；_decision_step_reward: 计算一次 DQN 决策对应的 reward。</t>
-  </si>
-  <si>
     <t>TransportGymWrapper</t>
   </si>
   <si>
@@ -698,13 +695,6 @@
   </si>
   <si>
     <t>cfg.env是参数集合来自配置文件：config/env/default.yaml，意思是读取配置文件里的 env 部分。</t>
-  </si>
-  <si>
-    <t>由于交通环境复杂，人和车各自有不同的出发阶段，不同阶段可选的动作也不同，人和车的动作空间也不同，所以中间需要一个 wrapper，把它变成 DQN 能训练的样子。
-Action ：所以 DQN 主要是在 routing 阶段选择目的地，departing 阶段由 wrapper 自动帮它沿最短路径开过去。
-Observation :_flatten_observation() 把原来像字典一样、分散存放的环境状态 obs，转化为具有含义的一维向量，然后拼接在一起，每一段都有固定含义， DQN通过这个向量感知当前状态。 
-如果开启 action mask，它返回的是一个 dict{  "features": flat_obs, "action_mask": mask}
-所以 DQN 的 step() 更像一个DQN的洁厕周期，而不是底层环境的一小步；此外，这里的reset()回答的是初始化后的交通世界，应该以什么形式呈现给 DQN.reset() 和 step() 最终还是依赖底层环境的 reset() 和 step()</t>
   </si>
   <si>
     <t>在 Stable-Baselines3 DQN 基础上加入 action mask，避免预测、探索和 target Q 计算时选择非法动作。读取 dqn_wrapper.py 提供的 action_mask；随机探索时只从合法动作中选；贪心选择时把非法动作的 Q 值设得极低；训练 TD target 时也用下一状态的 mask</t>
@@ -738,14 +728,46 @@
     <t>DQNTransportWrapper 负责告诉模型：哪些动作当前合法，生成action_mask，例如 [True, False, True, False, ...]，能不能选来自环境。
 MaskedDQN根据 mask 选动作，负责在选动作和算目标值时，不去选那些非法动作，在这里非法动作的 Q 值被压到很小，不参与 max。</t>
   </si>
+  <si>
+    <t>由于交通环境复杂，人和车各自有不同的出发阶段，不同阶段可选的动作也不同，人和车的动作空间也不同，所以中间需要一个 wrapper，把它变成 DQN 能训练的样子。
+Action ：所以 DQN 主要是在 routing 阶段选择目的地，departing 阶段由 wrapper 自动帮它沿最短路径开过去。
+Observation :_flatten_observation() 把原来像字典一样、分散存放的环境状态 obs，转化为具有含义的一维向量，然后拼接在一起，每一段都有固定含义， DQN通过这个向量感知当前状态。 
+如果开启 action mask，它返回的是一个 dict{  "features": flat_obs, "action_mask": mask}
+所以 DQN 的 step() 更像一个DQN的决策周期，而不是底层环境的一小步；此外，这里的reset()回答的是初始化后的交通世界，应该以什么形式呈现给 DQN.reset() 和 step() 最终还是依赖底层环境的 reset() 和 step()</t>
+  </si>
+  <si>
+    <r>
+      <t>action_masks: 返回合法动作；_format_observation/_flatten_observation: 整理 DQN 输入；reset: 重置并推进到决策点；step: 执行 DQN action 并自动推进内部阶段；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">_decision_step_reward: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>计算一次 DQN 决策对应的 reward。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -998,7 +1020,7 @@
     <col min="1" max="1" width="29.796875" customWidth="1"/>
     <col min="2" max="2" width="26.09765625" customWidth="1"/>
     <col min="3" max="3" width="22.09765625" customWidth="1"/>
-    <col min="4" max="4" width="36.69921875" customWidth="1"/>
+    <col min="4" max="4" width="49.69921875" customWidth="1"/>
     <col min="5" max="5" width="18.59765625" style="2" customWidth="1"/>
     <col min="6" max="6" width="44.796875" customWidth="1"/>
   </cols>
@@ -1034,13 +1056,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="19.95" customHeight="1">
@@ -1175,7 +1197,7 @@
         <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
@@ -1196,7 +1218,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>9</v>
@@ -1958,10 +1980,10 @@
         <v>175</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="22.05" customHeight="1">
@@ -1975,7 +1997,7 @@
         <v>177</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="22.05" customHeight="1">
@@ -1983,13 +2005,13 @@
         <v>44</v>
       </c>
       <c r="B4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" t="s">
         <v>179</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="22.05" customHeight="1">
@@ -1997,10 +2019,10 @@
         <v>48</v>
       </c>
       <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
         <v>182</v>
-      </c>
-      <c r="C5" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="22.05" customHeight="1">
@@ -2008,13 +2030,13 @@
         <v>56</v>
       </c>
       <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
         <v>184</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="22.05" customHeight="1">
@@ -2022,13 +2044,13 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" t="s">
         <v>187</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="22.05" customHeight="1">
@@ -2036,13 +2058,13 @@
         <v>89</v>
       </c>
       <c r="B8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" t="s">
         <v>190</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="22.05" customHeight="1">
@@ -2050,13 +2072,13 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" t="s">
         <v>193</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="22.05" customHeight="1">
@@ -2064,13 +2086,13 @@
         <v>74</v>
       </c>
       <c r="B10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" t="s">
         <v>196</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="22.05" customHeight="1">
@@ -2078,13 +2100,13 @@
         <v>74</v>
       </c>
       <c r="B11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" t="s">
         <v>199</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="22.05" customHeight="1">
@@ -2092,16 +2114,16 @@
         <v>74</v>
       </c>
       <c r="B12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" t="s">
         <v>202</v>
       </c>
-      <c r="C12" t="s">
-        <v>203</v>
-      </c>
       <c r="D12" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="22.05" customHeight="1">
@@ -2109,13 +2131,13 @@
         <v>74</v>
       </c>
       <c r="B13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" t="s">
         <v>204</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="22.05" customHeight="1">
@@ -2123,13 +2145,13 @@
         <v>78</v>
       </c>
       <c r="B14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" t="s">
         <v>207</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="22.05" customHeight="1">
@@ -2137,13 +2159,13 @@
         <v>78</v>
       </c>
       <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
         <v>210</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="22.05" customHeight="1">
@@ -2151,13 +2173,13 @@
         <v>78</v>
       </c>
       <c r="B16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" t="s">
         <v>213</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="22.05" customHeight="1">
@@ -2165,13 +2187,13 @@
         <v>82</v>
       </c>
       <c r="B17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C17" t="s">
         <v>216</v>
       </c>
-      <c r="C17" t="s">
-        <v>217</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22.05" customHeight="1">
@@ -2179,13 +2201,13 @@
         <v>82</v>
       </c>
       <c r="B18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18" t="s">
         <v>218</v>
       </c>
-      <c r="C18" t="s">
-        <v>219</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="22.05" customHeight="1">
@@ -2193,16 +2215,17 @@
         <v>82</v>
       </c>
       <c r="B19" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" t="s">
         <v>220</v>
       </c>
-      <c r="C19" t="s">
-        <v>221</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>